--- a/配送优化结果_含时间成本.xlsx
+++ b/配送优化结果_含时间成本.xlsx
@@ -85,28 +85,28 @@
     <t>五龙镇</t>
   </si>
   <si>
-    <t>中石阵村, 牛家岗村</t>
-  </si>
-  <si>
-    <t>碾上村, 西蒋村, 岭南村</t>
-  </si>
-  <si>
-    <t>石官村, 阳和村, 渔村, 岭后村, 罗圈村</t>
+    <t>碾上村, 七峪村, 西蒋村, 岭南村</t>
+  </si>
+  <si>
+    <t>石官村, 中石阵村, 牛家岗村</t>
+  </si>
+  <si>
+    <t>荷花村, 岭后村, 罗圈村</t>
+  </si>
+  <si>
+    <t>阳和村</t>
   </si>
   <si>
     <t>泽下村</t>
   </si>
   <si>
-    <t>七峪村</t>
+    <t>渔村</t>
   </si>
   <si>
     <t>合脉掌村</t>
   </si>
   <si>
     <t>桑峪村</t>
-  </si>
-  <si>
-    <t>荷花村</t>
   </si>
   <si>
     <t>上庄村</t>
@@ -581,16 +581,16 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>19.57719214806933</v>
+        <v>33.13852399188348</v>
       </c>
       <c r="E3">
-        <v>0.3915438429613865</v>
+        <v>0.6627704798376697</v>
       </c>
       <c r="F3">
-        <v>33.99148718284981</v>
+        <v>57.53775643662745</v>
       </c>
       <c r="G3">
-        <v>23.49263057768319</v>
+        <v>39.76622879026018</v>
       </c>
       <c r="H3">
         <v>20</v>
@@ -607,16 +607,16 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>17.48833465736105</v>
+        <v>26.47463322221351</v>
       </c>
       <c r="E4">
-        <v>0.349766693147221</v>
+        <v>0.5294926644442701</v>
       </c>
       <c r="F4">
-        <v>30.36464569888284</v>
+        <v>45.96737617106486</v>
       </c>
       <c r="G4">
-        <v>20.98600158883326</v>
+        <v>31.76955986665621</v>
       </c>
       <c r="H4">
         <v>20</v>
@@ -633,16 +633,16 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>28.74529370668357</v>
+        <v>17.81404345613414</v>
       </c>
       <c r="E5">
-        <v>0.5749058741336713</v>
+        <v>0.3562808691226828</v>
       </c>
       <c r="F5">
-        <v>49.90987855704054</v>
+        <v>30.93016737201658</v>
       </c>
       <c r="G5">
-        <v>34.49435244802028</v>
+        <v>21.37685214736097</v>
       </c>
       <c r="H5">
         <v>20</v>
@@ -656,22 +656,22 @@
         <v>17</v>
       </c>
       <c r="G6">
-        <v>2.37107182520712</v>
+        <v>2.429650098521379</v>
       </c>
       <c r="I6" t="s">
         <v>26</v>
       </c>
       <c r="J6">
-        <v>3.55660773781068</v>
+        <v>3.644475147782069</v>
       </c>
       <c r="K6">
-        <v>85</v>
+        <v>110.5</v>
       </c>
       <c r="L6">
-        <v>0.118553591260356</v>
+        <v>0.121482504926069</v>
       </c>
       <c r="M6">
-        <v>1.234898664164591</v>
+        <v>1.398535448803826</v>
       </c>
       <c r="N6">
         <v>10</v>
@@ -688,28 +688,28 @@
         <v>17</v>
       </c>
       <c r="G7">
-        <v>1.385232467768342</v>
+        <v>4.829722847977764</v>
       </c>
       <c r="I7" t="s">
         <v>27</v>
       </c>
       <c r="J7">
-        <v>4.155697403305025</v>
+        <v>7.244584271966645</v>
       </c>
       <c r="K7">
-        <v>73.5</v>
+        <v>85</v>
       </c>
       <c r="L7">
-        <v>0.06926162338841708</v>
+        <v>0.2414861423988882</v>
       </c>
       <c r="M7">
-        <v>0.9059991747597909</v>
+        <v>2.515410216530219</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -720,22 +720,22 @@
         <v>17</v>
       </c>
       <c r="G8">
-        <v>1.37942274005778</v>
+        <v>1.199102223633616</v>
       </c>
       <c r="I8" t="s">
         <v>28</v>
       </c>
       <c r="J8">
-        <v>4.138268220173339</v>
+        <v>3.597306670900848</v>
       </c>
       <c r="K8">
         <v>71</v>
       </c>
       <c r="L8">
-        <v>0.06897113700288898</v>
+        <v>0.0599551111816808</v>
       </c>
       <c r="M8">
-        <v>0.8873792001223194</v>
+        <v>0.771379462707946</v>
       </c>
       <c r="N8">
         <v>5</v>
@@ -752,22 +752,22 @@
         <v>17</v>
       </c>
       <c r="G9">
-        <v>1.537336619381264</v>
+        <v>1.555582336316758</v>
       </c>
       <c r="I9" t="s">
         <v>29</v>
       </c>
       <c r="J9">
-        <v>4.612009858143793</v>
+        <v>4.666747008950273</v>
       </c>
       <c r="K9">
-        <v>70.5</v>
+        <v>71</v>
       </c>
       <c r="L9">
-        <v>0.07686683096906322</v>
+        <v>0.07777911681583789</v>
       </c>
       <c r="M9">
-        <v>0.9856614518455233</v>
+        <v>1.000702227996729</v>
       </c>
       <c r="N9">
         <v>5</v>
@@ -784,22 +784,22 @@
         <v>17</v>
       </c>
       <c r="G10">
-        <v>1.199102223633616</v>
+        <v>1.537336619381264</v>
       </c>
       <c r="I10" t="s">
         <v>30</v>
       </c>
       <c r="J10">
-        <v>3.597306670900848</v>
+        <v>4.612009858143793</v>
       </c>
       <c r="K10">
-        <v>66</v>
+        <v>70.5</v>
       </c>
       <c r="L10">
-        <v>0.0599551111816808</v>
+        <v>0.07686683096906322</v>
       </c>
       <c r="M10">
-        <v>0.7456137536776187</v>
+        <v>0.9856614518455233</v>
       </c>
       <c r="N10">
         <v>5</v>
